--- a/research/traditional_assets/database/data/colombia/colombia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0258</v>
+        <v>0.0512</v>
       </c>
       <c r="E2">
-        <v>-0.008625000000000001</v>
+        <v>0.105</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0001828739225204617</v>
+        <v>0.0001976222576317594</v>
       </c>
       <c r="J2">
-        <v>0.0001292827954384539</v>
+        <v>0.0001491073437068871</v>
       </c>
       <c r="K2">
-        <v>2978.7</v>
+        <v>3487.1</v>
       </c>
       <c r="L2">
-        <v>0.207110177858742</v>
+        <v>0.2544084279950681</v>
       </c>
       <c r="M2">
-        <v>1036</v>
+        <v>672.04</v>
       </c>
       <c r="N2">
-        <v>0.04590611402086158</v>
+        <v>0.04562792371356603</v>
       </c>
       <c r="O2">
-        <v>0.3478027327357572</v>
+        <v>0.1927217458633248</v>
       </c>
       <c r="P2">
-        <v>972.3000000000001</v>
+        <v>659.1</v>
       </c>
       <c r="Q2">
-        <v>0.04308350836147077</v>
+        <v>0.04474936688234536</v>
       </c>
       <c r="R2">
-        <v>0.3264175647094371</v>
+        <v>0.1890109259843423</v>
       </c>
       <c r="S2">
-        <v>63.69999999999999</v>
+        <v>12.94</v>
       </c>
       <c r="T2">
-        <v>0.06148648648648648</v>
+        <v>0.01925480626153205</v>
       </c>
       <c r="U2">
-        <v>21646.4</v>
+        <v>12099.7</v>
       </c>
       <c r="V2">
-        <v>0.9591719175107898</v>
+        <v>0.821504952915057</v>
       </c>
       <c r="W2">
-        <v>0.1287224454104875</v>
+        <v>0.1328916668085904</v>
       </c>
       <c r="X2">
-        <v>0.09909524941303632</v>
+        <v>0.1576139384644555</v>
       </c>
       <c r="Y2">
-        <v>0.0296271959974512</v>
+        <v>-0.02472227165586513</v>
       </c>
       <c r="Z2">
-        <v>0.3615625820820528</v>
+        <v>0.2921915160130134</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05258820677568593</v>
+        <v>0.07984631172006321</v>
       </c>
       <c r="AC2">
-        <v>-0.05258820677568593</v>
+        <v>-0.07984631172006321</v>
       </c>
       <c r="AD2">
-        <v>49956.5</v>
+        <v>43834.1</v>
       </c>
       <c r="AE2">
-        <v>3.99935335763108</v>
+        <v>3.056255006593819</v>
       </c>
       <c r="AF2">
-        <v>49960.49935335763</v>
+        <v>43837.15625500659</v>
       </c>
       <c r="AG2">
-        <v>28314.09935335763</v>
+        <v>31737.45625500659</v>
       </c>
       <c r="AH2">
-        <v>0.6888414563527852</v>
+        <v>0.7485104642563661</v>
       </c>
       <c r="AI2">
-        <v>0.6131401611359429</v>
+        <v>0.6487746582118739</v>
       </c>
       <c r="AJ2">
-        <v>0.55646702880971</v>
+        <v>0.6830230605008775</v>
       </c>
       <c r="AK2">
-        <v>0.473190315949478</v>
+        <v>0.5721609404119951</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>14564.57725947522</v>
+        <v>13203.0421686747</v>
       </c>
       <c r="AP2">
-        <v>8254.839461620299</v>
+        <v>9559.474775604396</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Banco Bilbao Vizcaya Argentaria Colombia S.A. (BVC:BBVACOL)</t>
+          <t>Grupo Aval Acciones y Valores S.A. (BVC:GRUPOAVAL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.285</v>
+        <v>0.0814</v>
       </c>
       <c r="E3">
-        <v>0.0755</v>
+        <v>0.105</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>195.3</v>
+        <v>780.3</v>
       </c>
       <c r="L3">
-        <v>0.2650291762790067</v>
+        <v>0.1736701535722235</v>
       </c>
       <c r="M3">
-        <v>86.5</v>
+        <v>161.37</v>
       </c>
       <c r="N3">
-        <v>0.07515204170286707</v>
+        <v>0.06079339963833635</v>
       </c>
       <c r="O3">
-        <v>0.4429083461341526</v>
+        <v>0.206805074971165</v>
       </c>
       <c r="P3">
-        <v>86.5</v>
+        <v>154.9</v>
       </c>
       <c r="Q3">
-        <v>0.07515204170286707</v>
+        <v>0.05835593731163351</v>
       </c>
       <c r="R3">
-        <v>0.4429083461341526</v>
+        <v>0.1985133922850186</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>6.469999999999999</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.04009419346842659</v>
       </c>
       <c r="U3">
-        <v>1878.8</v>
+        <v>3915.3</v>
       </c>
       <c r="V3">
-        <v>1.632319721980886</v>
+        <v>1.4750226039783</v>
       </c>
       <c r="W3">
-        <v>0.1417477137465525</v>
+        <v>0.1328916668085904</v>
       </c>
       <c r="X3">
-        <v>0.1072927658838388</v>
+        <v>0.2372247413630041</v>
       </c>
       <c r="Y3">
-        <v>0.03445494786271368</v>
+        <v>-0.1043330745544138</v>
       </c>
       <c r="Z3">
-        <v>0.2392221789378003</v>
+        <v>0.3465644379994446</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05085730631293571</v>
+        <v>0.07343269564202716</v>
       </c>
       <c r="AC3">
-        <v>-0.05085730631293571</v>
+        <v>-0.07343269564202716</v>
       </c>
       <c r="AD3">
-        <v>2755.6</v>
+        <v>15784.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2755.6</v>
+        <v>15784.1</v>
       </c>
       <c r="AG3">
-        <v>876.8</v>
+        <v>11868.8</v>
       </c>
       <c r="AH3">
-        <v>0.7053703988122664</v>
+        <v>0.8560403503538792</v>
       </c>
       <c r="AI3">
-        <v>0.6382840730102844</v>
+        <v>0.6999011169790572</v>
       </c>
       <c r="AJ3">
-        <v>0.432389782029786</v>
+        <v>0.8172303624545555</v>
       </c>
       <c r="AK3">
-        <v>0.3595800524934383</v>
+        <v>0.6368543618471181</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grupo Aval Acciones y Valores S.A. (BVC:GRUPOAVAL)</t>
+          <t>Banco de Occidente S.A. (BVC:OCCIDENTE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.06269999999999999</v>
+        <v>0.0281</v>
       </c>
       <c r="E4">
-        <v>0.0378</v>
+        <v>0.0124</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,85 +856,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>829.6</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="L4">
-        <v>0.1614698898361166</v>
+        <v>0.1961624821392121</v>
       </c>
       <c r="M4">
-        <v>367.8</v>
+        <v>24.8</v>
       </c>
       <c r="N4">
-        <v>0.062802014855289</v>
+        <v>0.03156421025836834</v>
       </c>
       <c r="O4">
-        <v>0.4433461909353906</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="P4">
-        <v>331.8</v>
+        <v>24.8</v>
       </c>
       <c r="Q4">
-        <v>0.05665499871937164</v>
+        <v>0.03156421025836834</v>
       </c>
       <c r="R4">
-        <v>0.3999517839922854</v>
+        <v>0.2580645161290323</v>
       </c>
       <c r="S4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.09787928221859706</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>9434.200000000001</v>
+        <v>668.2</v>
       </c>
       <c r="V4">
-        <v>1.610893878596432</v>
+        <v>0.8504518263968436</v>
       </c>
       <c r="W4">
-        <v>0.1534988713318284</v>
+        <v>0.07179142387569103</v>
       </c>
       <c r="X4">
-        <v>0.1265196250598955</v>
+        <v>0.1576139384644555</v>
       </c>
       <c r="Y4">
-        <v>0.02697924627193293</v>
+        <v>-0.08582251458876446</v>
       </c>
       <c r="Z4">
-        <v>0.4899115111755284</v>
+        <v>0.1699136038401376</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05093652999254353</v>
+        <v>0.07980000119247393</v>
       </c>
       <c r="AC4">
-        <v>-0.05093652999254353</v>
+        <v>-0.07980000119247393</v>
       </c>
       <c r="AD4">
-        <v>18715.2</v>
+        <v>2312.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>18715.2</v>
+        <v>2312.6</v>
       </c>
       <c r="AG4">
-        <v>9281</v>
+        <v>1644.4</v>
       </c>
       <c r="AH4">
-        <v>0.7616567026294477</v>
+        <v>0.7464093212406803</v>
       </c>
       <c r="AI4">
-        <v>0.6496370887960928</v>
+        <v>0.6787192204971678</v>
       </c>
       <c r="AJ4">
-        <v>0.6131131296449216</v>
+        <v>0.6766799720176124</v>
       </c>
       <c r="AK4">
-        <v>0.4790317169475341</v>
+        <v>0.6003431784162681</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0217</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="E5">
-        <v>-0.111</v>
+        <v>0.0414</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,28 +978,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>190.6</v>
+        <v>280.3</v>
       </c>
       <c r="L5">
-        <v>0.1155641787424968</v>
+        <v>0.1649599811676083</v>
       </c>
       <c r="M5">
-        <v>31.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="N5">
-        <v>0.02085402184707051</v>
+        <v>0.0770856395290329</v>
       </c>
       <c r="O5">
-        <v>0.1652675760755509</v>
+        <v>0.2732786300392436</v>
       </c>
       <c r="P5">
-        <v>31.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>0.02085402184707051</v>
+        <v>0.0770856395290329</v>
       </c>
       <c r="R5">
-        <v>0.1652675760755509</v>
+        <v>0.2732786300392436</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +1008,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2644.7</v>
+        <v>2420.5</v>
       </c>
       <c r="V5">
-        <v>1.750877192982456</v>
+        <v>2.435845828720942</v>
       </c>
       <c r="W5">
-        <v>0.06850201265094882</v>
+        <v>0.09511367492365118</v>
       </c>
       <c r="X5">
-        <v>0.2075785107299619</v>
+        <v>0.3384252398823573</v>
       </c>
       <c r="Y5">
-        <v>-0.1390764980790131</v>
+        <v>-0.2433115649587061</v>
       </c>
       <c r="Z5">
-        <v>0.181967629113938</v>
+        <v>0.1733700642791552</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05108618708139097</v>
+        <v>0.07984631172006321</v>
       </c>
       <c r="AC5">
-        <v>-0.05108618708139097</v>
+        <v>-0.07984631172006321</v>
       </c>
       <c r="AD5">
-        <v>9931.299999999999</v>
+        <v>9702.299999999999</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>9931.299999999999</v>
+        <v>9702.299999999999</v>
       </c>
       <c r="AG5">
-        <v>7286.599999999999</v>
+        <v>7281.799999999999</v>
       </c>
       <c r="AH5">
-        <v>0.8679840584523414</v>
+        <v>0.907096110695587</v>
       </c>
       <c r="AI5">
-        <v>0.6861143926989851</v>
+        <v>0.6984443500608294</v>
       </c>
       <c r="AJ5">
-        <v>0.8282956883518433</v>
+        <v>0.8799226632831852</v>
       </c>
       <c r="AK5">
-        <v>0.6159425190194421</v>
+        <v>0.6348118701398333</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banco Comercial AV Villas S.A. (BVC:VILLAS)</t>
+          <t>Bancolombia S.A. (BVC:BCOLOMBIA)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.062</v>
+        <v>0.0471</v>
       </c>
       <c r="E6">
-        <v>-0.016</v>
+        <v>0.183</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,28 +1100,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>54.1</v>
+        <v>1431.4</v>
       </c>
       <c r="L6">
-        <v>0.1961566352429296</v>
+        <v>0.3266246805403432</v>
       </c>
       <c r="M6">
-        <v>16.2</v>
+        <v>352.7</v>
       </c>
       <c r="N6">
-        <v>0.06413301662707839</v>
+        <v>0.04648618726275833</v>
       </c>
       <c r="O6">
-        <v>0.299445471349353</v>
+        <v>0.2464021237948861</v>
       </c>
       <c r="P6">
-        <v>16.2</v>
+        <v>352.7</v>
       </c>
       <c r="Q6">
-        <v>0.06413301662707839</v>
+        <v>0.04648618726275833</v>
       </c>
       <c r="R6">
-        <v>0.299445471349353</v>
+        <v>0.2464021237948861</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,55 +1130,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>219.2</v>
+        <v>3447.4</v>
       </c>
       <c r="V6">
-        <v>0.8677751385589865</v>
+        <v>0.4543705187684521</v>
       </c>
       <c r="W6">
-        <v>0.1156971770744226</v>
+        <v>0.1799597686698517</v>
       </c>
       <c r="X6">
-        <v>0.09089773294223386</v>
+        <v>0.113483258983588</v>
       </c>
       <c r="Y6">
-        <v>0.02479944413218872</v>
+        <v>0.06647650968626362</v>
       </c>
       <c r="Z6">
-        <v>0.8255013469021251</v>
+        <v>0.3532000290142411</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05409022646998089</v>
+        <v>0.08127855416476873</v>
       </c>
       <c r="AC6">
-        <v>-0.05409022646998089</v>
+        <v>-0.08127855416476873</v>
       </c>
       <c r="AD6">
-        <v>432.1</v>
+        <v>9701.700000000001</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>432.1</v>
+        <v>9701.700000000001</v>
       </c>
       <c r="AG6">
-        <v>212.9</v>
+        <v>6254.300000000001</v>
       </c>
       <c r="AH6">
-        <v>0.6310793048050241</v>
+        <v>0.5611519529871767</v>
       </c>
       <c r="AI6">
-        <v>0.4656751805151417</v>
+        <v>0.5441131108281969</v>
       </c>
       <c r="AJ6">
-        <v>0.4573576799140709</v>
+        <v>0.4518513166925551</v>
       </c>
       <c r="AK6">
-        <v>0.3004091999435586</v>
+        <v>0.4348427646719368</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0107</v>
+        <v>0.0512</v>
       </c>
       <c r="E7">
-        <v>-0.0213</v>
+        <v>0.138</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1216,91 +1216,91 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.0007693586054156042</v>
+        <v>0.001025186964908499</v>
       </c>
       <c r="J7">
-        <v>0.0006393778976031204</v>
+        <v>0.0008305015533301971</v>
       </c>
       <c r="K7">
-        <v>1084.6</v>
+        <v>899</v>
       </c>
       <c r="L7">
-        <v>0.3172643772304452</v>
+        <v>0.3402467640602528</v>
       </c>
       <c r="M7">
-        <v>353.5</v>
+        <v>56.57</v>
       </c>
       <c r="N7">
-        <v>0.06104616022242561</v>
+        <v>0.02089227019241423</v>
       </c>
       <c r="O7">
-        <v>0.3259266088880693</v>
+        <v>0.06292547274749721</v>
       </c>
       <c r="P7">
-        <v>325.8</v>
+        <v>50.1</v>
       </c>
       <c r="Q7">
-        <v>0.05626262800697671</v>
+        <v>0.0185027883443513</v>
       </c>
       <c r="R7">
-        <v>0.3003872395353126</v>
+        <v>0.05572858731924361</v>
       </c>
       <c r="S7">
-        <v>27.69999999999999</v>
+        <v>6.469999999999999</v>
       </c>
       <c r="T7">
-        <v>0.07835926449787833</v>
+        <v>0.1143715750397737</v>
       </c>
       <c r="U7">
-        <v>3865.1</v>
+        <v>1648.3</v>
       </c>
       <c r="V7">
-        <v>0.6674668002141365</v>
+        <v>0.6087454297004838</v>
       </c>
       <c r="W7">
-        <v>0.1920971998370556</v>
+        <v>0.1397568634766657</v>
       </c>
       <c r="X7">
-        <v>0.08309081688339023</v>
+        <v>0.1416229815120812</v>
       </c>
       <c r="Y7">
-        <v>0.1090063829536654</v>
+        <v>-0.001866118035415476</v>
       </c>
       <c r="Z7">
-        <v>0.6662509853298737</v>
+        <v>0.2984303799355075</v>
       </c>
       <c r="AA7">
-        <v>0.0004259861542762221</v>
+        <v>0.0002478468940973598</v>
       </c>
       <c r="AB7">
-        <v>0.05512788742828911</v>
+        <v>0.08169947695047419</v>
       </c>
       <c r="AC7">
-        <v>-0.05470190127401289</v>
+        <v>-0.08145163005637683</v>
       </c>
       <c r="AD7">
-        <v>8017</v>
+        <v>6333.4</v>
       </c>
       <c r="AE7">
-        <v>3.99935335763108</v>
+        <v>3.056255006593819</v>
       </c>
       <c r="AF7">
-        <v>8020.999353357631</v>
+        <v>6336.456255006594</v>
       </c>
       <c r="AG7">
-        <v>4155.89935335763</v>
+        <v>4688.156255006594</v>
       </c>
       <c r="AH7">
-        <v>0.5807394983158044</v>
+        <v>0.700613310556074</v>
       </c>
       <c r="AI7">
-        <v>0.5542273369824292</v>
+        <v>0.6407997539326488</v>
       </c>
       <c r="AJ7">
-        <v>0.417821127172951</v>
+        <v>0.6338895853786999</v>
       </c>
       <c r="AK7">
-        <v>0.391796178736308</v>
+        <v>0.5689471175828571</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1309,132 +1309,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>2337.31778425656</v>
+        <v>1907.650602409639</v>
       </c>
       <c r="AP7">
-        <v>1211.632464535752</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bancolombia S.A. (BVC:BCOLOMBIA)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0299</v>
-      </c>
-      <c r="E8">
-        <v>-0.00125</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>624.5</v>
-      </c>
-      <c r="L8">
-        <v>0.1973892155003477</v>
-      </c>
-      <c r="M8">
-        <v>180.5</v>
-      </c>
-      <c r="N8">
-        <v>0.02254418285143321</v>
-      </c>
-      <c r="O8">
-        <v>0.289031224979984</v>
-      </c>
-      <c r="P8">
-        <v>180.5</v>
-      </c>
-      <c r="Q8">
-        <v>0.02254418285143321</v>
-      </c>
-      <c r="R8">
-        <v>0.289031224979984</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>3604.4</v>
-      </c>
-      <c r="V8">
-        <v>0.45018422531693</v>
-      </c>
-      <c r="W8">
-        <v>0.08589741826334539</v>
-      </c>
-      <c r="X8">
-        <v>0.08013999662968896</v>
-      </c>
-      <c r="Y8">
-        <v>0.005757421633656432</v>
-      </c>
-      <c r="Z8">
-        <v>0.2708408238738508</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.05492125057653816</v>
-      </c>
-      <c r="AC8">
-        <v>-0.05492125057653816</v>
-      </c>
-      <c r="AD8">
-        <v>10105.3</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>10105.3</v>
-      </c>
-      <c r="AG8">
-        <v>6500.9</v>
-      </c>
-      <c r="AH8">
-        <v>0.5579401274307357</v>
-      </c>
-      <c r="AI8">
-        <v>0.5467614610893784</v>
-      </c>
-      <c r="AJ8">
-        <v>0.4481092408012463</v>
-      </c>
-      <c r="AK8">
-        <v>0.4369559810992291</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
+        <v>1412.095257532107</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/colombia/colombia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0512</v>
+        <v>-0.02729</v>
       </c>
       <c r="E2">
-        <v>0.105</v>
+        <v>-0.31</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0001976222576317594</v>
+        <v>1.925784842587494e-05</v>
       </c>
       <c r="J2">
-        <v>0.0001491073437068871</v>
+        <v>1.547451454204137e-05</v>
       </c>
       <c r="K2">
-        <v>3487.1</v>
+        <v>2310.3</v>
       </c>
       <c r="L2">
-        <v>0.2544084279950681</v>
+        <v>0.1650697704327696</v>
       </c>
       <c r="M2">
-        <v>672.04</v>
+        <v>1578.71</v>
       </c>
       <c r="N2">
-        <v>0.04562792371356603</v>
+        <v>0.08687261661723354</v>
       </c>
       <c r="O2">
-        <v>0.1927217458633248</v>
+        <v>0.6833354975544301</v>
       </c>
       <c r="P2">
-        <v>659.1</v>
+        <v>1574.97</v>
       </c>
       <c r="Q2">
-        <v>0.04474936688234536</v>
+        <v>0.08666681340692357</v>
       </c>
       <c r="R2">
-        <v>0.1890109259843423</v>
+        <v>0.6817166601740033</v>
       </c>
       <c r="S2">
-        <v>12.94</v>
+        <v>3.740000000000009</v>
       </c>
       <c r="T2">
-        <v>0.01925480626153205</v>
+        <v>0.002369022809762407</v>
       </c>
       <c r="U2">
-        <v>12099.7</v>
+        <v>20152.3</v>
       </c>
       <c r="V2">
-        <v>0.821504952915057</v>
+        <v>1.108932629713801</v>
       </c>
       <c r="W2">
-        <v>0.1328916668085904</v>
+        <v>0.02481368563685637</v>
       </c>
       <c r="X2">
-        <v>0.1576139384644555</v>
+        <v>0.1121114061359012</v>
       </c>
       <c r="Y2">
-        <v>-0.02472227165586513</v>
+        <v>-0.08729772049904488</v>
       </c>
       <c r="Z2">
-        <v>0.2921915160130134</v>
+        <v>0.2503908702341104</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07984631172006321</v>
+        <v>0.06727613709010791</v>
       </c>
       <c r="AC2">
-        <v>-0.07984631172006321</v>
+        <v>-0.06727613709010791</v>
       </c>
       <c r="AD2">
-        <v>43834.1</v>
+        <v>53403</v>
       </c>
       <c r="AE2">
-        <v>3.056255006593819</v>
+        <v>0.3073453960814846</v>
       </c>
       <c r="AF2">
-        <v>43837.15625500659</v>
+        <v>53403.30734539608</v>
       </c>
       <c r="AG2">
-        <v>31737.45625500659</v>
+        <v>33251.00734539608</v>
       </c>
       <c r="AH2">
-        <v>0.7485104642563661</v>
+        <v>0.7461062627829169</v>
       </c>
       <c r="AI2">
-        <v>0.6487746582118739</v>
+        <v>0.6271695935345282</v>
       </c>
       <c r="AJ2">
-        <v>0.6830230605008775</v>
+        <v>0.6466085208921254</v>
       </c>
       <c r="AK2">
-        <v>0.5721609404119951</v>
+        <v>0.5115743643234922</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>13203.0421686747</v>
+        <v>161338.3685800604</v>
       </c>
       <c r="AP2">
-        <v>9559.474775604396</v>
+        <v>100456.2155450033</v>
       </c>
     </row>
     <row r="3">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0814</v>
+        <v>-0.0522</v>
       </c>
       <c r="E3">
-        <v>0.105</v>
+        <v>-0.334</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>780.3</v>
+        <v>80.5</v>
       </c>
       <c r="L3">
-        <v>0.1736701535722235</v>
+        <v>0.02733353706155988</v>
       </c>
       <c r="M3">
-        <v>161.37</v>
+        <v>130.64</v>
       </c>
       <c r="N3">
-        <v>0.06079339963833635</v>
+        <v>0.0443614384189616</v>
       </c>
       <c r="O3">
-        <v>0.206805074971165</v>
+        <v>1.622857142857143</v>
       </c>
       <c r="P3">
-        <v>154.9</v>
+        <v>126.9</v>
       </c>
       <c r="Q3">
-        <v>0.05835593731163351</v>
+        <v>0.04309144622907399</v>
       </c>
       <c r="R3">
-        <v>0.1985133922850186</v>
+        <v>1.57639751552795</v>
       </c>
       <c r="S3">
-        <v>6.469999999999999</v>
+        <v>3.740000000000009</v>
       </c>
       <c r="T3">
-        <v>0.04009419346842659</v>
+        <v>0.02862829148805885</v>
       </c>
       <c r="U3">
-        <v>3915.3</v>
+        <v>4543.9</v>
       </c>
       <c r="V3">
-        <v>1.4750226039783</v>
+        <v>1.542972596692587</v>
       </c>
       <c r="W3">
-        <v>0.1328916668085904</v>
+        <v>0.02208989627353054</v>
       </c>
       <c r="X3">
-        <v>0.2372247413630041</v>
+        <v>0.178656159672721</v>
       </c>
       <c r="Y3">
-        <v>-0.1043330745544138</v>
+        <v>-0.1565662633991904</v>
       </c>
       <c r="Z3">
-        <v>0.3465644379994446</v>
+        <v>0.1960289673717701</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07343269564202716</v>
+        <v>0.06256104895631794</v>
       </c>
       <c r="AC3">
-        <v>-0.07343269564202716</v>
+        <v>-0.06256104895631794</v>
       </c>
       <c r="AD3">
-        <v>15784.1</v>
+        <v>17267.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15784.1</v>
+        <v>17267.1</v>
       </c>
       <c r="AG3">
-        <v>11868.8</v>
+        <v>12723.2</v>
       </c>
       <c r="AH3">
-        <v>0.8560403503538792</v>
+        <v>0.8542994260835147</v>
       </c>
       <c r="AI3">
-        <v>0.6999011169790572</v>
+        <v>0.6943166647901823</v>
       </c>
       <c r="AJ3">
-        <v>0.8172303624545555</v>
+        <v>0.8120448554706697</v>
       </c>
       <c r="AK3">
-        <v>0.6368543618471181</v>
+        <v>0.6259784603425287</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banco de Occidente S.A. (BVC:OCCIDENTE)</t>
+          <t>BAC Holding International Corp. (BVC:BHI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,12 +837,6 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0281</v>
-      </c>
-      <c r="E4">
-        <v>0.0124</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -856,28 +850,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>96.09999999999999</v>
+        <v>517.4</v>
       </c>
       <c r="L4">
-        <v>0.1961624821392121</v>
+        <v>0.2298840360776647</v>
       </c>
       <c r="M4">
-        <v>24.8</v>
+        <v>278</v>
       </c>
       <c r="N4">
-        <v>0.03156421025836834</v>
+        <v>0.1152618267755711</v>
       </c>
       <c r="O4">
-        <v>0.2580645161290323</v>
+        <v>0.5373018940858137</v>
       </c>
       <c r="P4">
-        <v>24.8</v>
+        <v>278</v>
       </c>
       <c r="Q4">
-        <v>0.03156421025836834</v>
+        <v>0.1152618267755711</v>
       </c>
       <c r="R4">
-        <v>0.2580645161290323</v>
+        <v>0.5373018940858137</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>668.2</v>
+        <v>4051.3</v>
       </c>
       <c r="V4">
-        <v>0.8504518263968436</v>
+        <v>1.679713089265724</v>
       </c>
       <c r="W4">
-        <v>0.07179142387569103</v>
+        <v>0.1493174800150068</v>
       </c>
       <c r="X4">
-        <v>0.1576139384644555</v>
+        <v>0.1010551092320551</v>
       </c>
       <c r="Y4">
-        <v>-0.08582251458876446</v>
+        <v>0.0482623707829517</v>
       </c>
       <c r="Z4">
-        <v>0.1699136038401376</v>
+        <v>0.3368353312680525</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07980000119247393</v>
+        <v>0.06631709986396352</v>
       </c>
       <c r="AC4">
-        <v>-0.07980000119247393</v>
+        <v>-0.06631709986396352</v>
       </c>
       <c r="AD4">
-        <v>2312.6</v>
+        <v>4236.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2312.6</v>
+        <v>4236.2</v>
       </c>
       <c r="AG4">
-        <v>1644.4</v>
+        <v>184.8999999999996</v>
       </c>
       <c r="AH4">
-        <v>0.7464093212406803</v>
+        <v>0.6372046148523638</v>
       </c>
       <c r="AI4">
-        <v>0.6787192204971678</v>
+        <v>0.5264125855877126</v>
       </c>
       <c r="AJ4">
-        <v>0.6766799720176124</v>
+        <v>0.07120301910043117</v>
       </c>
       <c r="AK4">
-        <v>0.6003431784162681</v>
+        <v>0.04627127127127119</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.08169999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="E5">
-        <v>0.0414</v>
+        <v>-0.31</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,28 +972,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>280.3</v>
+        <v>40.5</v>
       </c>
       <c r="L5">
-        <v>0.1649599811676083</v>
+        <v>0.02463503649635037</v>
       </c>
       <c r="M5">
-        <v>76.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N5">
-        <v>0.0770856395290329</v>
+        <v>0.07560137457044673</v>
       </c>
       <c r="O5">
-        <v>0.2732786300392436</v>
+        <v>2.281481481481482</v>
       </c>
       <c r="P5">
-        <v>76.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="Q5">
-        <v>0.0770856395290329</v>
+        <v>0.07560137457044673</v>
       </c>
       <c r="R5">
-        <v>0.2732786300392436</v>
+        <v>2.281481481481482</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,55 +1002,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2420.5</v>
+        <v>3273.7</v>
       </c>
       <c r="V5">
-        <v>2.435845828720942</v>
+        <v>2.678530518736704</v>
       </c>
       <c r="W5">
-        <v>0.09511367492365118</v>
+        <v>0.01501056298876987</v>
       </c>
       <c r="X5">
-        <v>0.3384252398823573</v>
+        <v>0.2326576051528314</v>
       </c>
       <c r="Y5">
-        <v>-0.2433115649587061</v>
+        <v>-0.2176470421640615</v>
       </c>
       <c r="Z5">
-        <v>0.1733700642791552</v>
+        <v>0.1705341120089624</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07984631172006321</v>
+        <v>0.06724050152804537</v>
       </c>
       <c r="AC5">
-        <v>-0.07984631172006321</v>
+        <v>-0.06724050152804537</v>
       </c>
       <c r="AD5">
-        <v>9702.299999999999</v>
+        <v>10659.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>9702.299999999999</v>
+        <v>10659.3</v>
       </c>
       <c r="AG5">
-        <v>7281.799999999999</v>
+        <v>7385.599999999999</v>
       </c>
       <c r="AH5">
-        <v>0.907096110695587</v>
+        <v>0.897134200227244</v>
       </c>
       <c r="AI5">
-        <v>0.6984443500608294</v>
+        <v>0.6934456624272192</v>
       </c>
       <c r="AJ5">
-        <v>0.8799226632831852</v>
+        <v>0.8580125002904343</v>
       </c>
       <c r="AK5">
-        <v>0.6348118701398333</v>
+        <v>0.610491163682653</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bancolombia S.A. (BVC:BCOLOMBIA)</t>
+          <t>Banco Bilbao Vizcaya Argentaria Colombia S.A. (BVC:BBVACOL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0471</v>
+        <v>-0.00238</v>
       </c>
       <c r="E6">
-        <v>0.183</v>
+        <v>-0.149</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,28 +1094,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1431.4</v>
+        <v>75.5</v>
       </c>
       <c r="L6">
-        <v>0.3266246805403432</v>
+        <v>0.1125521765056649</v>
       </c>
       <c r="M6">
-        <v>352.7</v>
+        <v>172.6</v>
       </c>
       <c r="N6">
-        <v>0.04648618726275833</v>
+        <v>0.1938454627133872</v>
       </c>
       <c r="O6">
-        <v>0.2464021237948861</v>
+        <v>2.286092715231788</v>
       </c>
       <c r="P6">
-        <v>352.7</v>
+        <v>172.6</v>
       </c>
       <c r="Q6">
-        <v>0.04648618726275833</v>
+        <v>0.1938454627133872</v>
       </c>
       <c r="R6">
-        <v>0.2464021237948861</v>
+        <v>2.286092715231788</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1130,55 +1124,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3447.4</v>
+        <v>2143.5</v>
       </c>
       <c r="V6">
-        <v>0.4543705187684521</v>
+        <v>2.407345013477089</v>
       </c>
       <c r="W6">
-        <v>0.1799597686698517</v>
+        <v>0.05345511186632682</v>
       </c>
       <c r="X6">
-        <v>0.113483258983588</v>
+        <v>0.1718706161873423</v>
       </c>
       <c r="Y6">
-        <v>0.06647650968626362</v>
+        <v>-0.1184155043210155</v>
       </c>
       <c r="Z6">
-        <v>0.3532000290142411</v>
+        <v>0.1830236555619219</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.08127855416476873</v>
+        <v>0.06727613709010791</v>
       </c>
       <c r="AC6">
-        <v>-0.08127855416476873</v>
+        <v>-0.06727613709010791</v>
       </c>
       <c r="AD6">
-        <v>9701.700000000001</v>
+        <v>4901</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>9701.700000000001</v>
+        <v>4901</v>
       </c>
       <c r="AG6">
-        <v>6254.300000000001</v>
+        <v>2757.5</v>
       </c>
       <c r="AH6">
-        <v>0.5611519529871767</v>
+        <v>0.8462547915875264</v>
       </c>
       <c r="AI6">
-        <v>0.5441131108281969</v>
+        <v>0.729098482594466</v>
       </c>
       <c r="AJ6">
-        <v>0.4518513166925551</v>
+        <v>0.7559143616875462</v>
       </c>
       <c r="AK6">
-        <v>0.4348427646719368</v>
+        <v>0.602271486294638</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,124 +1189,365 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Banco Comercial AV Villas S.A. (BVC:VILLAS)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>-0.111</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>-51.7</v>
+      </c>
+      <c r="L7">
+        <v>-0.3887218045112782</v>
+      </c>
+      <c r="M7">
+        <v>8.67</v>
+      </c>
+      <c r="N7">
+        <v>0.05112028301886792</v>
+      </c>
+      <c r="O7">
+        <v>-0.1676982591876209</v>
+      </c>
+      <c r="P7">
+        <v>8.67</v>
+      </c>
+      <c r="Q7">
+        <v>0.05112028301886792</v>
+      </c>
+      <c r="R7">
+        <v>-0.1676982591876209</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>273</v>
+      </c>
+      <c r="V7">
+        <v>1.609669811320755</v>
+      </c>
+      <c r="W7">
+        <v>-0.1164676728993017</v>
+      </c>
+      <c r="X7">
+        <v>0.1107051198694748</v>
+      </c>
+      <c r="Y7">
+        <v>-0.2271727927687764</v>
+      </c>
+      <c r="Z7">
+        <v>0.2068750972157412</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06738283260815837</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06738283260815837</v>
+      </c>
+      <c r="AD7">
+        <v>384.5</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>384.5</v>
+      </c>
+      <c r="AG7">
+        <v>111.5</v>
+      </c>
+      <c r="AH7">
+        <v>0.6939180653311676</v>
+      </c>
+      <c r="AI7">
+        <v>0.468959629223076</v>
+      </c>
+      <c r="AJ7">
+        <v>0.3966559943080754</v>
+      </c>
+      <c r="AK7">
+        <v>0.2038763942219784</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bancolombia S.A. (BVC:BCOLOMBIA)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.292</v>
+      </c>
+      <c r="E8">
+        <v>0.198</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>1560.2</v>
+      </c>
+      <c r="L8">
+        <v>0.3051258482780201</v>
+      </c>
+      <c r="M8">
+        <v>790.5</v>
+      </c>
+      <c r="N8">
+        <v>0.09908746772293113</v>
+      </c>
+      <c r="O8">
+        <v>0.506665812075375</v>
+      </c>
+      <c r="P8">
+        <v>790.5</v>
+      </c>
+      <c r="Q8">
+        <v>0.09908746772293113</v>
+      </c>
+      <c r="R8">
+        <v>0.506665812075375</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>4307.2</v>
+      </c>
+      <c r="V8">
+        <v>0.5398982175537115</v>
+      </c>
+      <c r="W8">
+        <v>0.1965432969690862</v>
+      </c>
+      <c r="X8">
+        <v>0.09148314172145453</v>
+      </c>
+      <c r="Y8">
+        <v>0.1050601552476317</v>
+      </c>
+      <c r="Z8">
+        <v>0.4207784726793943</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06845361173863757</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06845361173863757</v>
+      </c>
+      <c r="AD8">
+        <v>9970.5</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>9970.5</v>
+      </c>
+      <c r="AG8">
+        <v>5663.3</v>
+      </c>
+      <c r="AH8">
+        <v>0.5555122212131511</v>
+      </c>
+      <c r="AI8">
+        <v>0.5116776746262682</v>
+      </c>
+      <c r="AJ8">
+        <v>0.4151644662087368</v>
+      </c>
+      <c r="AK8">
+        <v>0.3731083689644041</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Banco de Bogotá S.A. (BVC:BOGOTA)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.0512</v>
-      </c>
-      <c r="E7">
-        <v>0.138</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0.001025186964908499</v>
-      </c>
-      <c r="J7">
-        <v>0.0008305015533301971</v>
-      </c>
-      <c r="K7">
-        <v>899</v>
-      </c>
-      <c r="L7">
-        <v>0.3402467640602528</v>
-      </c>
-      <c r="M7">
-        <v>56.57</v>
-      </c>
-      <c r="N7">
-        <v>0.02089227019241423</v>
-      </c>
-      <c r="O7">
-        <v>0.06292547274749721</v>
-      </c>
-      <c r="P7">
-        <v>50.1</v>
-      </c>
-      <c r="Q7">
-        <v>0.0185027883443513</v>
-      </c>
-      <c r="R7">
-        <v>0.05572858731924361</v>
-      </c>
-      <c r="S7">
-        <v>6.469999999999999</v>
-      </c>
-      <c r="T7">
-        <v>0.1143715750397737</v>
-      </c>
-      <c r="U7">
-        <v>1648.3</v>
-      </c>
-      <c r="V7">
-        <v>0.6087454297004838</v>
-      </c>
-      <c r="W7">
-        <v>0.1397568634766657</v>
-      </c>
-      <c r="X7">
-        <v>0.1416229815120812</v>
-      </c>
-      <c r="Y7">
-        <v>-0.001866118035415476</v>
-      </c>
-      <c r="Z7">
-        <v>0.2984303799355075</v>
-      </c>
-      <c r="AA7">
-        <v>0.0002478468940973598</v>
-      </c>
-      <c r="AB7">
-        <v>0.08169947695047419</v>
-      </c>
-      <c r="AC7">
-        <v>-0.08145163005637683</v>
-      </c>
-      <c r="AD7">
-        <v>6333.4</v>
-      </c>
-      <c r="AE7">
-        <v>3.056255006593819</v>
-      </c>
-      <c r="AF7">
-        <v>6336.456255006594</v>
-      </c>
-      <c r="AG7">
-        <v>4688.156255006594</v>
-      </c>
-      <c r="AH7">
-        <v>0.700613310556074</v>
-      </c>
-      <c r="AI7">
-        <v>0.6407997539326488</v>
-      </c>
-      <c r="AJ7">
-        <v>0.6338895853786999</v>
-      </c>
-      <c r="AK7">
-        <v>0.5689471175828571</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>1907.650602409639</v>
-      </c>
-      <c r="AP7">
-        <v>1412.095257532107</v>
+      <c r="D9">
+        <v>-0.125</v>
+      </c>
+      <c r="E9">
+        <v>-0.316</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.0002175390805356764</v>
+      </c>
+      <c r="J9">
+        <v>0.0001825690524705461</v>
+      </c>
+      <c r="K9">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="L9">
+        <v>0.07094430992736078</v>
+      </c>
+      <c r="M9">
+        <v>105.9</v>
+      </c>
+      <c r="N9">
+        <v>0.04143354591337689</v>
+      </c>
+      <c r="O9">
+        <v>1.204778156996587</v>
+      </c>
+      <c r="P9">
+        <v>105.9</v>
+      </c>
+      <c r="Q9">
+        <v>0.04143354591337689</v>
+      </c>
+      <c r="R9">
+        <v>1.204778156996587</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1559.7</v>
+      </c>
+      <c r="V9">
+        <v>0.6102351422199617</v>
+      </c>
+      <c r="W9">
+        <v>0.02481368563685637</v>
+      </c>
+      <c r="X9">
+        <v>0.1121114061359012</v>
+      </c>
+      <c r="Y9">
+        <v>-0.08729772049904488</v>
+      </c>
+      <c r="Z9">
+        <v>0.1531481143935182</v>
+      </c>
+      <c r="AA9">
+        <v>2.796010613247542e-05</v>
+      </c>
+      <c r="AB9">
+        <v>0.06860648216787799</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06857852206174551</v>
+      </c>
+      <c r="AD9">
+        <v>5984.4</v>
+      </c>
+      <c r="AE9">
+        <v>0.3073453960814846</v>
+      </c>
+      <c r="AF9">
+        <v>5984.707345396081</v>
+      </c>
+      <c r="AG9">
+        <v>4425.007345396081</v>
+      </c>
+      <c r="AH9">
+        <v>0.7007355687206731</v>
+      </c>
+      <c r="AI9">
+        <v>0.6085787810679271</v>
+      </c>
+      <c r="AJ9">
+        <v>0.6338728085704189</v>
+      </c>
+      <c r="AK9">
+        <v>0.5347953176274022</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>18079.7583081571</v>
+      </c>
+      <c r="AP9">
+        <v>13368.60225195191</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/colombia/colombia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.02729</v>
+        <v>-0.02</v>
       </c>
       <c r="E2">
-        <v>-0.31</v>
+        <v>-0.06100000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1.925784842587494e-05</v>
+        <v>4.149466479629766E-05</v>
       </c>
       <c r="J2">
-        <v>1.547451454204137e-05</v>
+        <v>3.054995044281269E-05</v>
       </c>
       <c r="K2">
-        <v>2310.3</v>
+        <v>1648.3</v>
       </c>
       <c r="L2">
-        <v>0.1650697704327696</v>
+        <v>0.2606749746963563</v>
       </c>
       <c r="M2">
-        <v>1578.71</v>
+        <v>947.4000000000001</v>
       </c>
       <c r="N2">
-        <v>0.08687261661723354</v>
+        <v>0.0935518909844969</v>
       </c>
       <c r="O2">
-        <v>0.6833354975544301</v>
+        <v>0.5747740095856337</v>
       </c>
       <c r="P2">
-        <v>1574.97</v>
+        <v>947.4000000000001</v>
       </c>
       <c r="Q2">
-        <v>0.08666681340692357</v>
+        <v>0.0935518909844969</v>
       </c>
       <c r="R2">
-        <v>0.6817166601740033</v>
+        <v>0.5747740095856337</v>
       </c>
       <c r="S2">
-        <v>3.740000000000009</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.002369022809762407</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>20152.3</v>
+        <v>5880</v>
       </c>
       <c r="V2">
-        <v>1.108932629713801</v>
+        <v>0.5806260491754716</v>
       </c>
       <c r="W2">
-        <v>0.02481368563685637</v>
+        <v>0.1038654707395951</v>
       </c>
       <c r="X2">
-        <v>0.1121114061359012</v>
+        <v>0.1014300781882292</v>
       </c>
       <c r="Y2">
-        <v>-0.08729772049904488</v>
+        <v>0.002435392551365906</v>
       </c>
       <c r="Z2">
-        <v>0.2503908702341104</v>
+        <v>0.3011019214428985</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1.181196487096477E-05</v>
       </c>
       <c r="AB2">
-        <v>0.06727613709010791</v>
+        <v>0.07095618320003372</v>
       </c>
       <c r="AC2">
-        <v>-0.06727613709010791</v>
+        <v>-0.07094437123516276</v>
       </c>
       <c r="AD2">
-        <v>53403</v>
+        <v>13167</v>
       </c>
       <c r="AE2">
-        <v>0.3073453960814846</v>
+        <v>0.2981046778002533</v>
       </c>
       <c r="AF2">
-        <v>53403.30734539608</v>
+        <v>13167.2981046778</v>
       </c>
       <c r="AG2">
-        <v>33251.00734539608</v>
+        <v>7287.2981046778</v>
       </c>
       <c r="AH2">
-        <v>0.7461062627829169</v>
+        <v>0.5652584184124283</v>
       </c>
       <c r="AI2">
-        <v>0.6271695935345282</v>
+        <v>0.4841061142318475</v>
       </c>
       <c r="AJ2">
-        <v>0.6466085208921254</v>
+        <v>0.4184663694668405</v>
       </c>
       <c r="AK2">
-        <v>0.5115743643234922</v>
+        <v>0.3418185838368302</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>161338.3685800604</v>
+        <v>40891.30434782609</v>
       </c>
       <c r="AP2">
-        <v>100456.2155450033</v>
+        <v>22631.36057353354</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grupo Aval Acciones y Valores S.A. (BVC:GRUPOAVAL)</t>
+          <t>Banco de Bogotá S.A. (BVC:BOGOTA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0522</v>
+        <v>-0.15</v>
       </c>
       <c r="E3">
-        <v>-0.334</v>
+        <v>-0.228</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,97 +728,103 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.0002223928330564073</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.0001623639192494079</v>
       </c>
       <c r="K3">
-        <v>80.5</v>
+        <v>196.6</v>
       </c>
       <c r="L3">
-        <v>0.02733353706155988</v>
+        <v>0.1666384132903882</v>
       </c>
       <c r="M3">
-        <v>130.64</v>
+        <v>132.2</v>
       </c>
       <c r="N3">
-        <v>0.0443614384189616</v>
+        <v>0.06103416435826407</v>
       </c>
       <c r="O3">
-        <v>1.622857142857143</v>
+        <v>0.6724313326551373</v>
       </c>
       <c r="P3">
-        <v>126.9</v>
+        <v>132.2</v>
       </c>
       <c r="Q3">
-        <v>0.04309144622907399</v>
+        <v>0.06103416435826407</v>
       </c>
       <c r="R3">
-        <v>1.57639751552795</v>
+        <v>0.6724313326551373</v>
       </c>
       <c r="S3">
-        <v>3.740000000000009</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.02862829148805885</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>4543.9</v>
+        <v>1406.1</v>
       </c>
       <c r="V3">
-        <v>1.542972596692587</v>
+        <v>0.6491689750692521</v>
       </c>
       <c r="W3">
-        <v>0.02208989627353054</v>
+        <v>0.05126065757567856</v>
       </c>
       <c r="X3">
-        <v>0.178656159672721</v>
+        <v>0.1113983647522729</v>
       </c>
       <c r="Y3">
-        <v>-0.1565662633991904</v>
+        <v>-0.06013770717659432</v>
       </c>
       <c r="Z3">
-        <v>0.1960289673717701</v>
+        <v>0.1454998736858571</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.362392974192955E-05</v>
       </c>
       <c r="AB3">
-        <v>0.06256104895631794</v>
+        <v>0.07068276859452161</v>
       </c>
       <c r="AC3">
-        <v>-0.06256104895631794</v>
+        <v>-0.07065914466477968</v>
       </c>
       <c r="AD3">
-        <v>17267.1</v>
+        <v>4746.1</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.2981046778002533</v>
       </c>
       <c r="AF3">
-        <v>17267.1</v>
+        <v>4746.398104677801</v>
       </c>
       <c r="AG3">
-        <v>12723.2</v>
+        <v>3340.298104677801</v>
       </c>
       <c r="AH3">
-        <v>0.8542994260835147</v>
+        <v>0.6866499922025309</v>
       </c>
       <c r="AI3">
-        <v>0.6943166647901823</v>
+        <v>0.5440186064584848</v>
       </c>
       <c r="AJ3">
-        <v>0.8120448554706697</v>
+        <v>0.6066322674829567</v>
       </c>
       <c r="AK3">
-        <v>0.6259784603425287</v>
+        <v>0.4564122878318451</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>14739.44099378882</v>
+      </c>
+      <c r="AP3">
+        <v>10373.59659837826</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAC Holding International Corp. (BVC:BHI)</t>
+          <t>Bancolombia S.A. (BVC:BCOLOMBIA)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,6 +843,12 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.11</v>
+      </c>
+      <c r="E4">
+        <v>0.106</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -850,28 +862,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>517.4</v>
+        <v>1451.7</v>
       </c>
       <c r="L4">
-        <v>0.2298840360776647</v>
+        <v>0.2822452074503247</v>
       </c>
       <c r="M4">
-        <v>278</v>
+        <v>815.2</v>
       </c>
       <c r="N4">
-        <v>0.1152618267755711</v>
+        <v>0.1023991960808944</v>
       </c>
       <c r="O4">
-        <v>0.5373018940858137</v>
+        <v>0.5615485293104636</v>
       </c>
       <c r="P4">
-        <v>278</v>
+        <v>815.2</v>
       </c>
       <c r="Q4">
-        <v>0.1152618267755711</v>
+        <v>0.1023991960808944</v>
       </c>
       <c r="R4">
-        <v>0.5373018940858137</v>
+        <v>0.5615485293104636</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -880,674 +892,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>4051.3</v>
+        <v>4473.9</v>
       </c>
       <c r="V4">
-        <v>1.679713089265724</v>
+        <v>0.5619771385504333</v>
       </c>
       <c r="W4">
-        <v>0.1493174800150068</v>
+        <v>0.1564702839035116</v>
       </c>
       <c r="X4">
-        <v>0.1010551092320551</v>
+        <v>0.09146179162418551</v>
       </c>
       <c r="Y4">
-        <v>0.0482623707829517</v>
+        <v>0.0650084922793261</v>
       </c>
       <c r="Z4">
-        <v>0.3368353312680525</v>
+        <v>0.3989729746501598</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06631709986396352</v>
+        <v>0.07122959780554584</v>
       </c>
       <c r="AC4">
-        <v>-0.06631709986396352</v>
+        <v>-0.07122959780554584</v>
       </c>
       <c r="AD4">
-        <v>4236.2</v>
+        <v>8420.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4236.2</v>
+        <v>8420.9</v>
       </c>
       <c r="AG4">
-        <v>184.8999999999996</v>
+        <v>3947</v>
       </c>
       <c r="AH4">
-        <v>0.6372046148523638</v>
+        <v>0.5140368333343507</v>
       </c>
       <c r="AI4">
-        <v>0.5264125855877126</v>
+        <v>0.4558120652791686</v>
       </c>
       <c r="AJ4">
-        <v>0.07120301910043117</v>
+        <v>0.3314578434665771</v>
       </c>
       <c r="AK4">
-        <v>0.04627127127127119</v>
+        <v>0.281916489293316</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Grupo Bolívar S.A. (BVC:GRUBOLIVAR)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.0158</v>
-      </c>
-      <c r="E5">
-        <v>-0.31</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>40.5</v>
-      </c>
-      <c r="L5">
-        <v>0.02463503649635037</v>
-      </c>
-      <c r="M5">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="N5">
-        <v>0.07560137457044673</v>
-      </c>
-      <c r="O5">
-        <v>2.281481481481482</v>
-      </c>
-      <c r="P5">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="Q5">
-        <v>0.07560137457044673</v>
-      </c>
-      <c r="R5">
-        <v>2.281481481481482</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>3273.7</v>
-      </c>
-      <c r="V5">
-        <v>2.678530518736704</v>
-      </c>
-      <c r="W5">
-        <v>0.01501056298876987</v>
-      </c>
-      <c r="X5">
-        <v>0.2326576051528314</v>
-      </c>
-      <c r="Y5">
-        <v>-0.2176470421640615</v>
-      </c>
-      <c r="Z5">
-        <v>0.1705341120089624</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06724050152804537</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06724050152804537</v>
-      </c>
-      <c r="AD5">
-        <v>10659.3</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>10659.3</v>
-      </c>
-      <c r="AG5">
-        <v>7385.599999999999</v>
-      </c>
-      <c r="AH5">
-        <v>0.897134200227244</v>
-      </c>
-      <c r="AI5">
-        <v>0.6934456624272192</v>
-      </c>
-      <c r="AJ5">
-        <v>0.8580125002904343</v>
-      </c>
-      <c r="AK5">
-        <v>0.610491163682653</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Banco Bilbao Vizcaya Argentaria Colombia S.A. (BVC:BBVACOL)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>-0.00238</v>
-      </c>
-      <c r="E6">
-        <v>-0.149</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>75.5</v>
-      </c>
-      <c r="L6">
-        <v>0.1125521765056649</v>
-      </c>
-      <c r="M6">
-        <v>172.6</v>
-      </c>
-      <c r="N6">
-        <v>0.1938454627133872</v>
-      </c>
-      <c r="O6">
-        <v>2.286092715231788</v>
-      </c>
-      <c r="P6">
-        <v>172.6</v>
-      </c>
-      <c r="Q6">
-        <v>0.1938454627133872</v>
-      </c>
-      <c r="R6">
-        <v>2.286092715231788</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>2143.5</v>
-      </c>
-      <c r="V6">
-        <v>2.407345013477089</v>
-      </c>
-      <c r="W6">
-        <v>0.05345511186632682</v>
-      </c>
-      <c r="X6">
-        <v>0.1718706161873423</v>
-      </c>
-      <c r="Y6">
-        <v>-0.1184155043210155</v>
-      </c>
-      <c r="Z6">
-        <v>0.1830236555619219</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.06727613709010791</v>
-      </c>
-      <c r="AC6">
-        <v>-0.06727613709010791</v>
-      </c>
-      <c r="AD6">
-        <v>4901</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>4901</v>
-      </c>
-      <c r="AG6">
-        <v>2757.5</v>
-      </c>
-      <c r="AH6">
-        <v>0.8462547915875264</v>
-      </c>
-      <c r="AI6">
-        <v>0.729098482594466</v>
-      </c>
-      <c r="AJ6">
-        <v>0.7559143616875462</v>
-      </c>
-      <c r="AK6">
-        <v>0.602271486294638</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Banco Comercial AV Villas S.A. (BVC:VILLAS)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>-0.111</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>-51.7</v>
-      </c>
-      <c r="L7">
-        <v>-0.3887218045112782</v>
-      </c>
-      <c r="M7">
-        <v>8.67</v>
-      </c>
-      <c r="N7">
-        <v>0.05112028301886792</v>
-      </c>
-      <c r="O7">
-        <v>-0.1676982591876209</v>
-      </c>
-      <c r="P7">
-        <v>8.67</v>
-      </c>
-      <c r="Q7">
-        <v>0.05112028301886792</v>
-      </c>
-      <c r="R7">
-        <v>-0.1676982591876209</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>273</v>
-      </c>
-      <c r="V7">
-        <v>1.609669811320755</v>
-      </c>
-      <c r="W7">
-        <v>-0.1164676728993017</v>
-      </c>
-      <c r="X7">
-        <v>0.1107051198694748</v>
-      </c>
-      <c r="Y7">
-        <v>-0.2271727927687764</v>
-      </c>
-      <c r="Z7">
-        <v>0.2068750972157412</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.06738283260815837</v>
-      </c>
-      <c r="AC7">
-        <v>-0.06738283260815837</v>
-      </c>
-      <c r="AD7">
-        <v>384.5</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>384.5</v>
-      </c>
-      <c r="AG7">
-        <v>111.5</v>
-      </c>
-      <c r="AH7">
-        <v>0.6939180653311676</v>
-      </c>
-      <c r="AI7">
-        <v>0.468959629223076</v>
-      </c>
-      <c r="AJ7">
-        <v>0.3966559943080754</v>
-      </c>
-      <c r="AK7">
-        <v>0.2038763942219784</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Bancolombia S.A. (BVC:BCOLOMBIA)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.292</v>
-      </c>
-      <c r="E8">
-        <v>0.198</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>1560.2</v>
-      </c>
-      <c r="L8">
-        <v>0.3051258482780201</v>
-      </c>
-      <c r="M8">
-        <v>790.5</v>
-      </c>
-      <c r="N8">
-        <v>0.09908746772293113</v>
-      </c>
-      <c r="O8">
-        <v>0.506665812075375</v>
-      </c>
-      <c r="P8">
-        <v>790.5</v>
-      </c>
-      <c r="Q8">
-        <v>0.09908746772293113</v>
-      </c>
-      <c r="R8">
-        <v>0.506665812075375</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>4307.2</v>
-      </c>
-      <c r="V8">
-        <v>0.5398982175537115</v>
-      </c>
-      <c r="W8">
-        <v>0.1965432969690862</v>
-      </c>
-      <c r="X8">
-        <v>0.09148314172145453</v>
-      </c>
-      <c r="Y8">
-        <v>0.1050601552476317</v>
-      </c>
-      <c r="Z8">
-        <v>0.4207784726793943</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.06845361173863757</v>
-      </c>
-      <c r="AC8">
-        <v>-0.06845361173863757</v>
-      </c>
-      <c r="AD8">
-        <v>9970.5</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>9970.5</v>
-      </c>
-      <c r="AG8">
-        <v>5663.3</v>
-      </c>
-      <c r="AH8">
-        <v>0.5555122212131511</v>
-      </c>
-      <c r="AI8">
-        <v>0.5116776746262682</v>
-      </c>
-      <c r="AJ8">
-        <v>0.4151644662087368</v>
-      </c>
-      <c r="AK8">
-        <v>0.3731083689644041</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Banco de Bogotá S.A. (BVC:BOGOTA)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>-0.125</v>
-      </c>
-      <c r="E9">
-        <v>-0.316</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0.0002175390805356764</v>
-      </c>
-      <c r="J9">
-        <v>0.0001825690524705461</v>
-      </c>
-      <c r="K9">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="L9">
-        <v>0.07094430992736078</v>
-      </c>
-      <c r="M9">
-        <v>105.9</v>
-      </c>
-      <c r="N9">
-        <v>0.04143354591337689</v>
-      </c>
-      <c r="O9">
-        <v>1.204778156996587</v>
-      </c>
-      <c r="P9">
-        <v>105.9</v>
-      </c>
-      <c r="Q9">
-        <v>0.04143354591337689</v>
-      </c>
-      <c r="R9">
-        <v>1.204778156996587</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>1559.7</v>
-      </c>
-      <c r="V9">
-        <v>0.6102351422199617</v>
-      </c>
-      <c r="W9">
-        <v>0.02481368563685637</v>
-      </c>
-      <c r="X9">
-        <v>0.1121114061359012</v>
-      </c>
-      <c r="Y9">
-        <v>-0.08729772049904488</v>
-      </c>
-      <c r="Z9">
-        <v>0.1531481143935182</v>
-      </c>
-      <c r="AA9">
-        <v>2.796010613247542e-05</v>
-      </c>
-      <c r="AB9">
-        <v>0.06860648216787799</v>
-      </c>
-      <c r="AC9">
-        <v>-0.06857852206174551</v>
-      </c>
-      <c r="AD9">
-        <v>5984.4</v>
-      </c>
-      <c r="AE9">
-        <v>0.3073453960814846</v>
-      </c>
-      <c r="AF9">
-        <v>5984.707345396081</v>
-      </c>
-      <c r="AG9">
-        <v>4425.007345396081</v>
-      </c>
-      <c r="AH9">
-        <v>0.7007355687206731</v>
-      </c>
-      <c r="AI9">
-        <v>0.6085787810679271</v>
-      </c>
-      <c r="AJ9">
-        <v>0.6338728085704189</v>
-      </c>
-      <c r="AK9">
-        <v>0.5347953176274022</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>18079.7583081571</v>
-      </c>
-      <c r="AP9">
-        <v>13368.60225195191</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/colombia/colombia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/colombia/colombia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.02</v>
+        <v>-0.08449999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.06100000000000001</v>
+        <v>-0.182</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4.149466479629766E-05</v>
+        <v>1.822013572028397E-05</v>
       </c>
       <c r="J2">
-        <v>3.054995044281269E-05</v>
+        <v>1.561439658185287E-05</v>
       </c>
       <c r="K2">
-        <v>1648.3</v>
+        <v>2623.6</v>
       </c>
       <c r="L2">
-        <v>0.2606749746963563</v>
+        <v>0.1821881184681087</v>
       </c>
       <c r="M2">
-        <v>947.4000000000001</v>
+        <v>1518.4587</v>
       </c>
       <c r="N2">
-        <v>0.0935518909844969</v>
+        <v>0.08423153346054851</v>
       </c>
       <c r="O2">
-        <v>0.5747740095856337</v>
+        <v>0.5787691340143315</v>
       </c>
       <c r="P2">
-        <v>947.4000000000001</v>
+        <v>1518.4587</v>
       </c>
       <c r="Q2">
-        <v>0.0935518909844969</v>
+        <v>0.08423153346054851</v>
       </c>
       <c r="R2">
-        <v>0.5747740095856337</v>
+        <v>0.5787691340143315</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,55 +636,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5880</v>
+        <v>20513.84</v>
       </c>
       <c r="V2">
-        <v>0.5806260491754716</v>
+        <v>1.137938226679684</v>
       </c>
       <c r="W2">
-        <v>0.1038654707395951</v>
+        <v>0.04981969485110947</v>
       </c>
       <c r="X2">
-        <v>0.1014300781882292</v>
+        <v>0.1339811915155645</v>
       </c>
       <c r="Y2">
-        <v>0.002435392551365906</v>
+        <v>-0.08416149666445501</v>
       </c>
       <c r="Z2">
-        <v>0.3011019214428985</v>
+        <v>0.2389962713392178</v>
       </c>
       <c r="AA2">
-        <v>1.181196487096477E-05</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07095618320003372</v>
+        <v>0.06887756450123328</v>
       </c>
       <c r="AC2">
-        <v>-0.07094437123516276</v>
+        <v>-0.06887756450123328</v>
       </c>
       <c r="AD2">
-        <v>13167</v>
+        <v>51567.9</v>
       </c>
       <c r="AE2">
         <v>0.2981046778002533</v>
       </c>
       <c r="AF2">
-        <v>13167.2981046778</v>
+        <v>51568.1981046778</v>
       </c>
       <c r="AG2">
-        <v>7287.2981046778</v>
+        <v>31054.3581046778</v>
       </c>
       <c r="AH2">
-        <v>0.5652584184124283</v>
+        <v>0.7409713789856414</v>
       </c>
       <c r="AI2">
-        <v>0.4841061142318475</v>
+        <v>0.5988635391169812</v>
       </c>
       <c r="AJ2">
-        <v>0.4184663694668405</v>
+        <v>0.6327092966047896</v>
       </c>
       <c r="AK2">
-        <v>0.3418185838368302</v>
+        <v>0.47341660945235</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>40891.30434782609</v>
+        <v>160148.7577639752</v>
       </c>
       <c r="AP2">
-        <v>22631.36057353354</v>
+        <v>96442.10591514845</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Banco de Bogotá S.A. (BVC:BOGOTA)</t>
+          <t>Grupo Aval Acciones y Valores S.A. (BVC:GRUPOAVAL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.15</v>
+        <v>-0.08449999999999999</v>
       </c>
       <c r="E3">
-        <v>-0.228</v>
+        <v>-0.238</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,34 +728,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.0002223928330564073</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.0001623639192494079</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>196.6</v>
+        <v>195.9</v>
       </c>
       <c r="L3">
-        <v>0.1666384132903882</v>
+        <v>0.07135312329266072</v>
       </c>
       <c r="M3">
-        <v>132.2</v>
+        <v>190.2</v>
       </c>
       <c r="N3">
-        <v>0.06103416435826407</v>
+        <v>0.0790031152647975</v>
       </c>
       <c r="O3">
-        <v>0.6724313326551373</v>
+        <v>0.9709035222052067</v>
       </c>
       <c r="P3">
-        <v>132.2</v>
+        <v>190.2</v>
       </c>
       <c r="Q3">
-        <v>0.06103416435826407</v>
+        <v>0.0790031152647975</v>
       </c>
       <c r="R3">
-        <v>0.6724313326551373</v>
+        <v>0.9709035222052067</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,67 +764,61 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1406.1</v>
+        <v>4245.3</v>
       </c>
       <c r="V3">
-        <v>0.6491689750692521</v>
+        <v>1.763364485981308</v>
       </c>
       <c r="W3">
-        <v>0.05126065757567856</v>
+        <v>0.04837873212654039</v>
       </c>
       <c r="X3">
-        <v>0.1113983647522729</v>
+        <v>0.1989860741571423</v>
       </c>
       <c r="Y3">
-        <v>-0.06013770717659432</v>
+        <v>-0.1506073420306019</v>
       </c>
       <c r="Z3">
-        <v>0.1454998736858571</v>
+        <v>0.1692027042850716</v>
       </c>
       <c r="AA3">
-        <v>2.362392974192955E-05</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07068276859452161</v>
+        <v>0.06465396279457994</v>
       </c>
       <c r="AC3">
-        <v>-0.07065914466477968</v>
+        <v>-0.06465396279457994</v>
       </c>
       <c r="AD3">
-        <v>4746.1</v>
+        <v>17269.8</v>
       </c>
       <c r="AE3">
-        <v>0.2981046778002533</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>4746.398104677801</v>
+        <v>17269.8</v>
       </c>
       <c r="AG3">
-        <v>3340.298104677801</v>
+        <v>13024.5</v>
       </c>
       <c r="AH3">
-        <v>0.6866499922025309</v>
+        <v>0.8776508972267537</v>
       </c>
       <c r="AI3">
-        <v>0.5440186064584848</v>
+        <v>0.6870817585040779</v>
       </c>
       <c r="AJ3">
-        <v>0.6066322674829567</v>
+        <v>0.84399300155521</v>
       </c>
       <c r="AK3">
-        <v>0.4564122878318451</v>
+        <v>0.6234890879237136</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>14739.44099378882</v>
-      </c>
-      <c r="AP3">
-        <v>10373.59659837826</v>
       </c>
     </row>
     <row r="4">
@@ -835,117 +829,843 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Grupo Bolívar S.A. (BVC:GRUBOLIVAR)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.0109</v>
+      </c>
+      <c r="E4">
+        <v>-0.182</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>121.5</v>
+      </c>
+      <c r="L4">
+        <v>0.07829112700560603</v>
+      </c>
+      <c r="M4">
+        <v>89.2</v>
+      </c>
+      <c r="N4">
+        <v>0.08224230130923844</v>
+      </c>
+      <c r="O4">
+        <v>0.7341563786008231</v>
+      </c>
+      <c r="P4">
+        <v>89.2</v>
+      </c>
+      <c r="Q4">
+        <v>0.08224230130923844</v>
+      </c>
+      <c r="R4">
+        <v>0.7341563786008231</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>2798.4</v>
+      </c>
+      <c r="V4">
+        <v>2.580121703853956</v>
+      </c>
+      <c r="W4">
+        <v>0.03942757009345794</v>
+      </c>
+      <c r="X4">
+        <v>0.2141072395487643</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1746796694553063</v>
+      </c>
+      <c r="Z4">
+        <v>0.1539445882808083</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.06656832033168539</v>
+      </c>
+      <c r="AC4">
+        <v>-0.06656832033168539</v>
+      </c>
+      <c r="AD4">
+        <v>8712.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>8712.9</v>
+      </c>
+      <c r="AG4">
+        <v>5914.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.889298290380199</v>
+      </c>
+      <c r="AI4">
+        <v>0.651607161553764</v>
+      </c>
+      <c r="AJ4">
+        <v>0.8450372190710234</v>
+      </c>
+      <c r="AK4">
+        <v>0.5593965761846212</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Banco de Occidente S.A. (BVC:OCCIDENTE)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0584</v>
+      </c>
+      <c r="E5">
+        <v>-0.009210000000000001</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>117.9</v>
+      </c>
+      <c r="L5">
+        <v>0.1881583147143313</v>
+      </c>
+      <c r="M5">
+        <v>46.7</v>
+      </c>
+      <c r="N5">
+        <v>0.07331240188383047</v>
+      </c>
+      <c r="O5">
+        <v>0.3960983884648007</v>
+      </c>
+      <c r="P5">
+        <v>46.7</v>
+      </c>
+      <c r="Q5">
+        <v>0.07331240188383047</v>
+      </c>
+      <c r="R5">
+        <v>0.3960983884648007</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1053.3</v>
+      </c>
+      <c r="V5">
+        <v>1.653532182103611</v>
+      </c>
+      <c r="W5">
+        <v>0.08787359320265335</v>
+      </c>
+      <c r="X5">
+        <v>0.1727039259506044</v>
+      </c>
+      <c r="Y5">
+        <v>-0.08483033274795106</v>
+      </c>
+      <c r="Z5">
+        <v>0.1955326439034132</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.06822578020484318</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06822578020484318</v>
+      </c>
+      <c r="AD5">
+        <v>3617.3</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>3617.3</v>
+      </c>
+      <c r="AG5">
+        <v>2564</v>
+      </c>
+      <c r="AH5">
+        <v>0.8502691394589004</v>
+      </c>
+      <c r="AI5">
+        <v>0.7161552167887547</v>
+      </c>
+      <c r="AJ5">
+        <v>0.8009996875976257</v>
+      </c>
+      <c r="AK5">
+        <v>0.6413687870525553</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Banco Bilbao Vizcaya Argentaria Colombia S.A. (BVC:BBVACOL)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.269</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>-57.5</v>
+      </c>
+      <c r="L6">
+        <v>-0.1186545604622369</v>
+      </c>
+      <c r="M6">
+        <v>6.64</v>
+      </c>
+      <c r="N6">
+        <v>0.008907968875771399</v>
+      </c>
+      <c r="O6">
+        <v>-0.1154782608695652</v>
+      </c>
+      <c r="P6">
+        <v>6.64</v>
+      </c>
+      <c r="Q6">
+        <v>0.008907968875771399</v>
+      </c>
+      <c r="R6">
+        <v>-0.1154782608695652</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1631.5</v>
+      </c>
+      <c r="V6">
+        <v>2.188757713979072</v>
+      </c>
+      <c r="W6">
+        <v>-0.03251710682576486</v>
+      </c>
+      <c r="X6">
+        <v>0.1565788232776913</v>
+      </c>
+      <c r="Y6">
+        <v>-0.1890959301034562</v>
+      </c>
+      <c r="Z6">
+        <v>0.09315647827758555</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.06835544503380925</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06835544503380925</v>
+      </c>
+      <c r="AD6">
+        <v>3549.3</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>3549.3</v>
+      </c>
+      <c r="AG6">
+        <v>1917.8</v>
+      </c>
+      <c r="AH6">
+        <v>0.8264372365939414</v>
+      </c>
+      <c r="AI6">
+        <v>0.6601383774132351</v>
+      </c>
+      <c r="AJ6">
+        <v>0.7201111444878342</v>
+      </c>
+      <c r="AK6">
+        <v>0.5120824544070919</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BAC Holding International Corp. (BVC:BHI)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>640.1</v>
+      </c>
+      <c r="L7">
+        <v>0.2538870379184516</v>
+      </c>
+      <c r="M7">
+        <v>233.6</v>
+      </c>
+      <c r="N7">
+        <v>0.07989875842254678</v>
+      </c>
+      <c r="O7">
+        <v>0.3649429776597407</v>
+      </c>
+      <c r="P7">
+        <v>233.6</v>
+      </c>
+      <c r="Q7">
+        <v>0.07989875842254678</v>
+      </c>
+      <c r="R7">
+        <v>0.3649429776597407</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>4901.1</v>
+      </c>
+      <c r="V7">
+        <v>1.676334781270308</v>
+      </c>
+      <c r="W7">
+        <v>0.1679832043038971</v>
+      </c>
+      <c r="X7">
+        <v>0.1033782753048748</v>
+      </c>
+      <c r="Y7">
+        <v>0.06460492899902236</v>
+      </c>
+      <c r="Z7">
+        <v>0.6310256795314612</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.0693996839686573</v>
+      </c>
+      <c r="AC7">
+        <v>-0.0693996839686573</v>
+      </c>
+      <c r="AD7">
+        <v>5075.7</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>5075.7</v>
+      </c>
+      <c r="AG7">
+        <v>174.5999999999995</v>
+      </c>
+      <c r="AH7">
+        <v>0.6345100882566193</v>
+      </c>
+      <c r="AI7">
+        <v>0.5404855712916622</v>
+      </c>
+      <c r="AJ7">
+        <v>0.05635348416873753</v>
+      </c>
+      <c r="AK7">
+        <v>0.03888728034031926</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Banco Comercial AV Villas S.A. (BVC:VILLAS)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.09210000000000002</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>-42.6</v>
+      </c>
+      <c r="L8">
+        <v>-0.2888135593220339</v>
+      </c>
+      <c r="M8">
+        <v>4.7187</v>
+      </c>
+      <c r="N8">
+        <v>0.04626176470588236</v>
+      </c>
+      <c r="O8">
+        <v>-0.1107676056338028</v>
+      </c>
+      <c r="P8">
+        <v>4.7187</v>
+      </c>
+      <c r="Q8">
+        <v>0.04626176470588236</v>
+      </c>
+      <c r="R8">
+        <v>-0.1107676056338028</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>4.24</v>
+      </c>
+      <c r="V8">
+        <v>0.0415686274509804</v>
+      </c>
+      <c r="W8">
+        <v>-0.09829257037378866</v>
+      </c>
+      <c r="X8">
+        <v>0.1031752914735408</v>
+      </c>
+      <c r="Y8">
+        <v>-0.2014678618473295</v>
+      </c>
+      <c r="Z8">
+        <v>0.2706918700679024</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06940810955805195</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06940810955805195</v>
+      </c>
+      <c r="AD8">
+        <v>175.9</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>175.9</v>
+      </c>
+      <c r="AG8">
+        <v>171.66</v>
+      </c>
+      <c r="AH8">
+        <v>0.6329614969413458</v>
+      </c>
+      <c r="AI8">
+        <v>0.3002218808670422</v>
+      </c>
+      <c r="AJ8">
+        <v>0.6272747204560404</v>
+      </c>
+      <c r="AK8">
+        <v>0.2951208609840801</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Banco de Bogotá S.A. (BVC:BOGOTA)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.15</v>
+      </c>
+      <c r="E9">
+        <v>-0.228</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.0002223928330564073</v>
+      </c>
+      <c r="J9">
+        <v>0.0001623639192494079</v>
+      </c>
+      <c r="K9">
+        <v>196.6</v>
+      </c>
+      <c r="L9">
+        <v>0.1666384132903882</v>
+      </c>
+      <c r="M9">
+        <v>132.2</v>
+      </c>
+      <c r="N9">
+        <v>0.06103416435826407</v>
+      </c>
+      <c r="O9">
+        <v>0.6724313326551373</v>
+      </c>
+      <c r="P9">
+        <v>132.2</v>
+      </c>
+      <c r="Q9">
+        <v>0.06103416435826407</v>
+      </c>
+      <c r="R9">
+        <v>0.6724313326551373</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1406.1</v>
+      </c>
+      <c r="V9">
+        <v>0.6491689750692521</v>
+      </c>
+      <c r="W9">
+        <v>0.05126065757567856</v>
+      </c>
+      <c r="X9">
+        <v>0.1113835597534377</v>
+      </c>
+      <c r="Y9">
+        <v>-0.06012290217775913</v>
+      </c>
+      <c r="Z9">
+        <v>0.1454998736858571</v>
+      </c>
+      <c r="AA9">
+        <v>2.362392974192955E-05</v>
+      </c>
+      <c r="AB9">
+        <v>0.07067812944802115</v>
+      </c>
+      <c r="AC9">
+        <v>-0.07065450551827923</v>
+      </c>
+      <c r="AD9">
+        <v>4746.1</v>
+      </c>
+      <c r="AE9">
+        <v>0.2981046778002533</v>
+      </c>
+      <c r="AF9">
+        <v>4746.398104677801</v>
+      </c>
+      <c r="AG9">
+        <v>3340.298104677801</v>
+      </c>
+      <c r="AH9">
+        <v>0.6866499922025309</v>
+      </c>
+      <c r="AI9">
+        <v>0.5440186064584848</v>
+      </c>
+      <c r="AJ9">
+        <v>0.6066322674829567</v>
+      </c>
+      <c r="AK9">
+        <v>0.4564122878318451</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>14739.44099378882</v>
+      </c>
+      <c r="AP9">
+        <v>10373.59659837826</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Bancolombia S.A. (BVC:BCOLOMBIA)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="D10">
         <v>0.11</v>
       </c>
-      <c r="E4">
+      <c r="E10">
         <v>0.106</v>
       </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
         <v>1451.7</v>
       </c>
-      <c r="L4">
+      <c r="L10">
         <v>0.2822452074503247</v>
       </c>
-      <c r="M4">
+      <c r="M10">
         <v>815.2</v>
       </c>
-      <c r="N4">
+      <c r="N10">
         <v>0.1023991960808944</v>
       </c>
-      <c r="O4">
+      <c r="O10">
         <v>0.5615485293104636</v>
       </c>
-      <c r="P4">
+      <c r="P10">
         <v>815.2</v>
       </c>
-      <c r="Q4">
+      <c r="Q10">
         <v>0.1023991960808944</v>
       </c>
-      <c r="R4">
+      <c r="R10">
         <v>0.5615485293104636</v>
       </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
         <v>4473.9</v>
       </c>
-      <c r="V4">
+      <c r="V10">
         <v>0.5619771385504333</v>
       </c>
-      <c r="W4">
+      <c r="W10">
         <v>0.1564702839035116</v>
       </c>
-      <c r="X4">
-        <v>0.09146179162418551</v>
-      </c>
-      <c r="Y4">
-        <v>0.0650084922793261</v>
-      </c>
-      <c r="Z4">
+      <c r="X10">
+        <v>0.09145148614211501</v>
+      </c>
+      <c r="Y10">
+        <v>0.0650187977613966</v>
+      </c>
+      <c r="Z10">
         <v>0.3989729746501598</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.07122959780554584</v>
-      </c>
-      <c r="AC4">
-        <v>-0.07122959780554584</v>
-      </c>
-      <c r="AD4">
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.07122458972084485</v>
+      </c>
+      <c r="AC10">
+        <v>-0.07122458972084485</v>
+      </c>
+      <c r="AD10">
         <v>8420.9</v>
       </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
         <v>8420.9</v>
       </c>
-      <c r="AG4">
+      <c r="AG10">
         <v>3947</v>
       </c>
-      <c r="AH4">
+      <c r="AH10">
         <v>0.5140368333343507</v>
       </c>
-      <c r="AI4">
+      <c r="AI10">
         <v>0.4558120652791686</v>
       </c>
-      <c r="AJ4">
+      <c r="AJ10">
         <v>0.3314578434665771</v>
       </c>
-      <c r="AK4">
+      <c r="AK10">
         <v>0.281916489293316</v>
       </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
         <v>0</v>
       </c>
     </row>
